--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,100 +36,224 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么 C store mask 不能修复 K 尾部的错误 load？</t>
+          <t xml:space="preserve">分块矩阵乘法怎样算出一个输出 tile？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：store mask 只能阻止越界写回，不能修复已经污染的有效 accumulator。
-• [T#B#K 维]：K 是归约维度；无效乘积会累加进有效输出元素。
-• [T#B#M/N 维]：M/N 的无效 lane 对应不写回的输出坐标，可在 store 时丢弃。
-[T#B,!c47f17#边界]：K 尾部必须在 load 时以 0 填充；C mask 只覆盖 M/N 输出边界。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：沿 K 轴分段相乘，把各段结果累加到同一个输出 tile。
+• [T#B#加载]：每轮读取 A 的 BLOCK_M×BLOCK_K tile 和 B 的 BLOCK_K×BLOCK_N tile。
+• [T#B#累加]：两块相乘得到 BLOCK_M×BLOCK_N 的部分和，加入同形状的 accumulator。
+• [T#B#推进]：沿 K 轴移到下一段，直至覆盖全部 K；输出 tile 的 M/N 坐标不变。
+[T#B,!c47f17#边界]：K 尾部不足整块时补零；本课以 FP16 输入配 FP32 累加，数据流本身不限定累加精度。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">归约前补零，写回时裁边界</t>
+          <t xml:space="preserve">固定 M/N，遍历 K，累加部分和</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 03 学习记录 · K 尾部纠错</t>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped PID 映射中，尾组为什么必须使用实际 group size？</t>
+          <t xml:space="preserve">移动 K 指针基址时，局部 offs_k 会变化吗？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它同时保证 program 不映射到越界 tile，也不遗漏合法 tile。
-• [T#B#越界]：固定使用完整组大小可能把末尾 PID 映射到不存在的 pid_m。
-• [T#B#漏块]：错误的除法与取模基数也会使某个合法 pid_n 组合无人计算。
-[T#B,!c47f17#边界]：只有最后不足 GROUP_SIZE_M 行的 group 需要缩小实际大小。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不会；变化的是指针基址，局部 offs_k 保持不变。
+• [T#B#第二轮]：BLOCK_K=4 时，局部 \[0,1,2,3\] 加到基址 4 上，对应全局 K 坐标 \[4,5,6,7\]。
+[T#B,!c47f17#边界]：这里绑定本课移动指针的写法；若 K=5，全局坐标 5、6、7 仍须在 load 时屏蔽并补零。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不越界，也不漏块</t>
+          <t xml:space="preserve">局部偏移不变，K 基址推进</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 03 学习记录 · 未公开变式</t>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录 · Triton 3.7.1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">benchmark 中候选差异小于运行状态漂移时，最多能下什么结论？</t>
+          <t xml:space="preserve">为什么 C store mask 救不了错误的 K 尾部？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只能说当前方法无法稳定区分候选影响与漂移，不能宣布胜负。
-• [T#B#不支持]：不能由证据不足反推某个候选更快，也不能证明真实影响一定很小。
-[T#B,!c47f17#边界]：结论必须限定设备、shape、launch 配置和测量方法。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错误 K 值已进入有效输出的累加和，写回时无法再剔除。
+• [T#B#归约]：每个有效 C\[i,j\] 都沿 K 求和；尾部多算的乘积会污染这个结果。
+• [T#B#写回]：C store mask 只按 M/N 坐标决定是否写出，不能分辨累加和里的错误来源。
+[T#B,!c47f17#边界]：K 尾部须在 load 时补零；M/N 输出边界才由最终 store mask 裁掉。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">分不出来，不等于差异很小</t>
+          <t xml:space="preserve">归约前补零，写回时裁边界</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 03 学习记录 · ABBA benchmark</t>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录；8/19 综合验收</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped ordering 在什么条件下更可能显著加速 matmul？</t>
+          <t xml:space="preserve">M/N 边界为何可以读取合法的 dummy 数据？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：当相邻 program 能复用 A/B tile，且复用前数据仍驻留 L2 时，收益最可能明显。
-• [T#B#网格]：M/N 都形成较大的二维 tile grid，才有足够重排空间。
-• [T#B#工作集]：工作集处于 cache-sensitive 区间，grouping 能缩短复用距离。
-• [T#B#配置]：group size 需匹配并发窗口、block 配置和目标架构。
-[T#B,!c47f17#边界]：小或狭长 grid、全命中、全不驻留、计算或 wrapper 开销主导时，收益可能很弱。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：这些计算只落在最终不写回的输出坐标，不能串入别的有效输出。
+• [T#B#独立]：M/N 指定不同 C 元素；每个 C 元素只沿 K 归约。
+• [T#B#裁剪]：无效 M/N lane 可读取合法 dummy 值保持 tile 形状，最后用 C mask 丢弃对应输出。
+[T#B,!c47f17#边界]：M/N load 用 mask 也可正确；取模不保证更快，且这一理由不能用于 K 归约维。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">复用距离落在 L2 驻留窗口内</t>
+          <t xml:space="preserve">无效输出可丢弃，归约污染不可丢弃</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 03 学习记录 · grouped ordering 高价值问题</t>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">组高为 2 时，组内 PID 沿哪一轴先变化？</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先遍历该组的 M 行，再推进 N 列。
+• [T#B#例子]：4×3 tile 网格的第一组依次为 (0,0)、(1,0)、(0,1)、(1,1)；因此 pid=2/3 共用 B 的同一列 tile。
+[T#B,!c47f17#边界]：尾组不足两行时，必须改用实际组高；这里描述的是 grouped PID 映射。</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">组内先 M，后 N</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录 · Triton 3.7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尾组为何必须使用实际组高？</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：这样才能把剩余 PID 映射到全部合法 tile，既不越界也不漏块。
+• [T#B#错配]：若尾组仅剩一行却仍按两行映射，下一个 PID 可能落到不存在的行。
+• [T#B#遗漏]：该 PID 本应负责的合法列 tile 因此无人计算；实际组高同时修复两类错误。
+[T#B,!c47f17#边界]：完整组仍用设定组高，只在最后不足整组时缩小。</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不越界，也不漏块</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录；8/19 尾组变式</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">为什么仅凭 shape 不能选出最快的 tile 配置？</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：tile 改变数据复用，也改变资源占用和无效工作；胜负取决于实际瓶颈。
+• [T#B#工作量]：program 数和 K-loop 次数只描述一部分开销，边界 tile 还可能浪费大量 lane。
+• [T#B#资源]：更大的 accumulator 影响寄存器占用与 occupancy，收益可能抵不过资源代价。
+• [T#B#测量]：结合 warps/stages、GPU 架构和编译结果，在目标设备比较候选。
+[T#B,!c47f17#边界]：“M/N 大、K 小”只能帮助提出候选，不能证明某个配置更快。</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">复用收益与资源代价共同决定性能</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 03 · 8/17 概念记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分不清配置差异与运行漂移，能下什么结论？</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：只能说当前方法证据不足，无法稳定区分配置的性能影响。
+• [T#B#不能推出]：既不能宣布某个配置更快，也不能据此证明真实影响很小。
+[T#B,!c47f17#边界]：限定设备、shape、launch 配置和测量方法；换条件需要重新验证。</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分不出来，不等于差异很小</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 03 · 8/19 实践记录 · ABBA 结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grouped ordering 怎样通过 L2 局部性获益？</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：通过重排缩短可复用 A/B tile 的访问间隔，让再次访问有机会命中仍驻留 L2 的数据。
+• [T#B#机会]：较大的二维 tile 网格提供重排空间；访存敏感时，减少输入流量更可能体现为收益。
+• [T#B#匹配]：group size 需与并发窗口、block 配置和目标架构相配，才能保住可复用数据。
+[T#B,!c47f17#边界]：具体收益需在目标设备、shape、分组配置和计时口径下验证，不能推广成单调加速规律。</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">复用赶在 L2 淘汰之前</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 03 · 8/19 实践记录 · grouped ordering</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-technical-qa.xlsx
@@ -36,16 +36,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">分块矩阵乘法怎样算出一个输出 tile？</t>
+          <t xml:space="preserve">计算 C=A×B，其中 A 的形状为 \[M,K\]、B 为 \[K,N\]。若一个 program 负责 C 的一个 \[BLOCK_M,BLOCK_N\] 输出块，它如何沿 K 轴完成这个块的计算？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：沿 K 轴分段相乘，把各段结果累加到同一个输出 tile。
-• [T#B#加载]：每轮读取 A 的 BLOCK_M×BLOCK_K tile 和 B 的 BLOCK_K×BLOCK_N tile。
-• [T#B#累加]：两块相乘得到 BLOCK_M×BLOCK_N 的部分和，加入同形状的 accumulator。
-• [T#B#推进]：沿 K 轴移到下一段，直至覆盖全部 K；输出 tile 的 M/N 坐标不变。
-[T#B,!c47f17#边界]：K 尾部不足整块时补零；本课以 FP16 输入配 FP32 累加，数据流本身不限定累加精度。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：固定输出块覆盖的 M 行和 N 列，沿共享的 K 轴逐段加载 A、B，并把每段矩阵乘法的结果累加到同一输出块。
+• [T#B#初始化]：为这块输出建立形状为 \[BLOCK_M,BLOCK_N\] 的 accumulator，并初始化为零。它的两个轴对应输出行和输出列，不包含 K 轴。
+• [T#B#每轮加载]：在当前 K 段，加载 A 的 \[BLOCK_M,BLOCK_K\] 块以及 B 的 \[BLOCK_K,BLOCK_N\] 块；两者共享同一段 K 坐标。
+• [T#B#乘加与推进]：两块相乘得到 \[BLOCK_M,BLOCK_N\] 的部分和并加入 accumulator，然后把 A 的列基址和 B 的行基址各推进 BLOCK_K；输出行列坐标保持不变。
+• [T#B#完成输出]：遍历全部 K 段后，accumulator 才包含完整点积，可以写回该 program 负责的 C 块。
+[T#B,!c47f17#边界]：K 尾部不足整块时，越界输入应补零，避免污染点积；M/N 尾部的无效输出不写回。FP16 输入配 FP32 累加是一种精度选择，并不是上述分块数据流的数学前提。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -62,14 +63,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">移动 K 指针基址时，局部 offs_k 会变化吗？</t>
+          <t xml:space="preserve">在 Triton 分块矩阵乘法中，offs_k=tl.arange(0,BLOCK_K) 表示块内 K 偏移。若 K 循环通过移动 A/B 指针基址推进，offs_k 本身会怎样变化？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不会；变化的是指针基址，局部 offs_k 保持不变。
-• [T#B#第二轮]：BLOCK_K=4 时，局部 \[0,1,2,3\] 加到基址 4 上，对应全局 K 坐标 \[4,5,6,7\]。
-[T#B,!c47f17#边界]：这里绑定本课移动指针的写法；若 K=5，全局坐标 5、6、7 仍须在 load 时屏蔽并补零。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：offs_k 本身保持不变；每轮变化的是 A/B 指针基址，因此同一组局部偏移会指向不同的全局 K 坐标。
+• [T#B#通用关系]：将循环轮次记作 t，从 0 开始计数，则该轮全局 K 坐标为 t×BLOCK_K+offs_k；局部 offsets 始终是 0 到 BLOCK_K−1。
+• [T#B#具体例子]：BLOCK_K=4 时，第二轮 t=1：offs_k 仍为 \[0,1,2,3\]，指针指向的全局 K 坐标则为 \[4,5,6,7\]。
+[T#B,!c47f17#边界]：如果总长度 K=5，第二轮只有全局坐标 4 有效，5、6、7 必须在 load 时屏蔽并补零。这里讨论的是移动指针基址的循环写法，不能把局部偏移和全局坐标混称为同一个量。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -86,15 +88,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么 C store mask 救不了错误的 K 尾部？</t>
+          <t xml:space="preserve">计算 C\[M,N\]=A\[M,K\]×B\[K,N\] 时，若 K 不是 BLOCK_K 的整数倍，为什么不能只靠最终写回 C 的 mask 来处理 K 尾部的越界读取？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：错误 K 值已进入有效输出的累加和，写回时无法再剔除。
-• [T#B#归约]：每个有效 C\[i,j\] 都沿 K 求和；尾部多算的乘积会污染这个结果。
-• [T#B#写回]：C store mask 只按 M/N 坐标决定是否写出，不能分辨累加和里的错误来源。
-[T#B,!c47f17#边界]：K 尾部须在 load 时补零；M/N 输出边界才由最终 store mask 裁掉。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 K 是每个有效输出元素内部的求和轴；错误的尾部输入会先进入有效结果的累加和，写回 mask 无法再把这些错误项剔除。
+[E##C_{ij}=\sum_{k=0}^{K-1}A_{ik}B_{kj}]
+• [T#B#污染发生的位置]：对合法的 i、j，如果最后一块仍把 k≥K 的数据参与乘加，得到的 accumulator 就已经不是上式的结果。
+• [T#B#写回 mask 的职责]：最终 mask 只判断输出行 i&lt;M、列 j&lt;N 是否有效。它能丢弃不存在的 C 元素，却不能检查一个合法 C 元素内部哪些乘积来自错误 K 坐标。
+[T#B,!c47f17#边界]：因此 K 尾部必须在读取 A/B 时屏蔽并补零，使额外乘积为零；M/N 输出边界才由最终 store mask 裁掉。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -111,15 +114,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">M/N 边界为何可以读取合法的 dummy 数据？</t>
+          <t xml:space="preserve">在分块矩阵乘法 C\[M,N\]=A\[M,K\]×B\[K,N\] 的边界块中，为什么可以让超出 M/N 的位置通过取模读取合法的替代输入，再丢弃对应输出？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：这些计算只落在最终不写回的输出坐标，不能串入别的有效输出。
-• [T#B#独立]：M/N 指定不同 C 元素；每个 C 元素只沿 K 归约。
-• [T#B#裁剪]：无效 M/N lane 可读取合法 dummy 值保持 tile 形状，最后用 C mask 丢弃对应输出。
-[T#B,!c47f17#边界]：M/N load 用 mask 也可正确；取模不保证更快，且这一理由不能用于 K 归约维。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 M/N 决定的是不同输出元素的位置，而不是同一个输出内部的求和项；无效行列位置的计算只会生成最终被丢弃的输出。
+• [T#B#替代输入的作用]：例如无效的 A 行号对 M 取模、无效的 B 列号对 N 取模，可以让读取落在合法地址，同时保留固定大小的输入 tile。这里的替代值只是为无效输出位置提供占位计算。
+• [T#B#为何不污染有效结果]：矩阵乘法的每个 C\[i,j\] 只沿 K 求和，不会把别的输出行或列加进自己。有效 i、j 的点积仍使用其本来对应的 A 行和 B 列。
+• [T#B#写回条件]：写回时必须用未经取模的原始输出行列号判断 i&lt;M 且 j&lt;N，丢弃替代位置算出的结果。
+[T#B,!c47f17#边界]：M/N load 直接用 mask 也能保证正确，取模并不保证更快。这个理由不能用于 K：K 若回绕并参与求和，就会把重复乘积加进有效输出。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -136,14 +140,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">组高为 2 时，组内 PID 沿哪一轴先变化？</t>
+          <t xml:space="preserve">Triton 矩阵乘法把输出划成 4 行、3 列的 tile 网格，并按 GROUP_SIZE_M=2 做 grouped PID 映射。第一组中，递增的 PID 怎样对应到输出 tile 坐标？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先遍历该组的 M 行，再推进 N 列。
-• [T#B#例子]：4×3 tile 网格的第一组依次为 (0,0)、(1,0)、(0,1)、(1,1)；因此 pid=2/3 共用 B 的同一列 tile。
-[T#B,!c47f17#边界]：尾组不足两行时，必须改用实际组高；这里描述的是 grouped PID 映射。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：在同一组内，先遍历组内的 M 行，再切换到下一个 N 列；因此第一组依次处理 (0,0)、(1,0)、(0,1)、(1,1)、(0,2)、(1,2)。
+• [T#B#坐标约定]：每个坐标写作 (输出 tile 行号,输出 tile 列号)，不是原矩阵中的单个元素坐标。这里第一组覆盖 tile 行 0、1，组高为 2。
+• [T#B#映射规律]：把组内线性编号记作 p，实际组高记作 h，则组内行号为 p%h，输出 tile 列号为 p//h；全局行号还需加上该组起始 tile 行号。
+• [T#B#复用关系]：pid=2 和 pid=3 分别负责 (0,1)、(1,1)：输出行不同、输出列相同，因此在相同 K 段需要同一个 B 列 tile。
+[T#B,!c47f17#边界]：这里描述的是线性 PID 到输出坐标的映射，不是 GPU 执行完成顺序的保证。最后一组若不足两行，必须改用实际组高。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -160,15 +166,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">尾组为何必须使用实际组高？</t>
+          <t xml:space="preserve">分块矩阵乘法按 GROUP_SIZE_M 个输出 tile 行分组时，若最后一组不足整组，为什么 PID 映射必须使用尾组的实际行数？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：这样才能把剩余 PID 映射到全部合法 tile，既不越界也不漏块。
-• [T#B#错配]：若尾组仅剩一行却仍按两行映射，下一个 PID 可能落到不存在的行。
-• [T#B#遗漏]：该 PID 本应负责的合法列 tile 因此无人计算；实际组高同时修复两类错误。
-[T#B,!c47f17#边界]：完整组仍用设定组高，只在最后不足整组时缩小。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为最后一组实际存在的行变少，组内 PID 对行号取模、对列号整除时也必须使用这个实际组高，否则会同时出现越界 tile 和遗漏 tile。
+• [T#B#实际组高]：设 tile 总行数为 num_pid_m，当前组的起始 tile 行号为 first_pid_m，则实际组高是 min(GROUP_SIZE_M,num_pid_m−first_pid_m)。
+• [T#B#具体例子]：tile 网格有 5 行、3 列，设定组高为 2。前两组覆盖行 0–3，尾组只有行 4，所以剩余 pid=12、13、14 应依次映射到 (4,0)、(4,1)、(4,2)。
+• [T#B#错误后果]：若尾组仍按两行计算，pid=13 会被映射到不存在的 (5,0)，pid=14 只到 (4,1)，导致必须计算的 (4,2) 没有 program 负责。
+[T#B,!c47f17#边界]：完整组继续使用设定组高；仅当剩余 tile 行数不足一组时缩小。实际组高保证的是输出覆盖正确性，不能仅靠 store mask 修复遗漏。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -185,16 +192,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">为什么仅凭 shape 不能选出最快的 tile 配置？</t>
+          <t xml:space="preserve">为同一个矩阵乘法 A\[M,K\]×B\[K,N\] 选择 BLOCK_M、BLOCK_N、BLOCK_K 时，为什么只比较输入 shape、program 数和 K 循环次数，仍不能确定哪组 tile 配置最快？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：tile 改变数据复用，也改变资源占用和无效工作；胜负取决于实际瓶颈。
-• [T#B#工作量]：program 数和 K-loop 次数只描述一部分开销，边界 tile 还可能浪费大量 lane。
-• [T#B#资源]：更大的 accumulator 影响寄存器占用与 occupancy，收益可能抵不过资源代价。
-• [T#B#测量]：结合 warps/stages、GPU 架构和编译结果，在目标设备比较候选。
-[T#B,!c47f17#边界]：“M/N 大、K 小”只能帮助提出候选，不能证明某个配置更快。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 tile 大小同时改变数据复用、无效工作量和硬件资源占用；program 更少或循环更短，只减少了部分开销，并不等于总延迟更低。
+• [T#B#边界工作量]：M/N 尾部不满时，大 tile 可能让更多输出位置参与计算却最终不写回；仅数 program 个数会忽略这些额外工作。
+• [T#B#资源占用]：更大的输出 tile 需要更大的 accumulator，可能提高寄存器占用，使能够同时驻留的 program/warp 变少。这会改变隐藏访存或执行延迟的机会，不能只根据输出块更大就判断更快。
+• [T#B#配置共同作用]：数据复用、warps/stages、GPU 架构和编译结果都会影响实际瓶颈；同样的 M/N/K 在不同配置和设备上可能得到不同胜负。
+[T#B,!c47f17#边界]：shape 分析适合筛选候选和提出预测。最终判断应在目标 GPU 上、相同输入和可比计时条件下测量，不能仅用“M/N 大、K 小”宣布某组配置更快。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -211,14 +218,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">分不清配置差异与运行漂移，能下什么结论？</t>
+          <t xml:space="preserve">比较同一矩阵乘法的两种 GROUP_SIZE_M 配置时，若多轮 benchmark 无法把配置造成的耗时差异与 GPU 运行状态漂移稳定区分，应该怎样表述性能结论？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只能说当前方法证据不足，无法稳定区分配置的性能影响。
-• [T#B#不能推出]：既不能宣布某个配置更快，也不能据此证明真实影响很小。
-[T#B,!c47f17#边界]：限定设备、shape、launch 配置和测量方法；换条件需要重新验证。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：应表述为：在当前设备、输入形状、launch 配置和测量方法下，证据不足以稳定区分两种分组配置的性能。
+• [T#B#为何证据不足]：运行状态随时间变化本身就会改变耗时；如果这种变化与配置间的差异混在一起，就不能把观测到的快慢可靠归因于 GROUP_SIZE_M。
+• [T#B#不能推出什么]：既不能据此宣布某个配置更快，也不能说“真实影响很小”。看不清一个差异，可能是测量噪声太大，而不是差异本身很小。
+[T#B,!c47f17#边界]：结论必须限定在已经测量的条件内；更换设备、shape 或测量方法后，需要重新验证，而不能把此次“分不出来”推广为普遍无收益。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -235,15 +243,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped ordering 怎样通过 L2 局部性获益？</t>
+          <t xml:space="preserve">分块矩阵乘法中，grouped ordering 通过重排线性 PID 到输出 tile 的映射，为什么可能提高 GPU 的 L2 cache 命中率并加速计算？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：通过重排缩短可复用 A/B tile 的访问间隔，让再次访问有机会命中仍驻留 L2 的数据。
-• [T#B#机会]：较大的二维 tile 网格提供重排空间；访存敏感时，减少输入流量更可能体现为收益。
-• [T#B#匹配]：group size 需与并发窗口、block 配置和目标架构相配，才能保住可复用数据。
-[T#B,!c47f17#边界]：具体收益需在目标设备、shape、分组配置和计时口径下验证，不能推广成单调加速规律。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它让需要相同 A/B 输入 tile 的 program 在映射上更接近，缩短数据再次被访问的间隔；如果数据此时仍在 L2 中，就可能减少重复从显存读取的流量。
+• [T#B#复用机会]：同一输出 tile 列的不同行，会在相同 K 段使用同一个 B tile；同一输出 tile 行的不同列，也会使用相同 A tile。分组排序尝试让这些复用更及时。
+• [T#B#缓存条件]：“访问间隔短”必须短到数据尚未被其他访问从 L2 淘汰，才可能转化为命中收益。较大的二维 tile 网格提供更多重排空间。
+• [T#B#何时更有帮助]：当计算对访存较敏感，且 group size 与并发窗口、block 配置和目标架构匹配时，减少显存流量更有机会降低耗时。
+[T#B,!c47f17#边界]：PID 映射不强制实际调度顺序；L2 容量和并发访问也会改变数据驻留。因此 grouped ordering 不能保证每次更快，更不能推出 group size 越大越快。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-03-matrix-multiplication-technical-qa.xlsx
@@ -42,11 +42,11 @@
       <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：固定输出块覆盖的 M 行和 N 列，沿共享的 K 轴逐段加载 A、B，并把每段矩阵乘法的结果累加到同一输出块。
-• [T#B#初始化]：为这块输出建立形状为 \[BLOCK_M,BLOCK_N\] 的 accumulator，并初始化为零。它的两个轴对应输出行和输出列，不包含 K 轴。
+• [T#B#初始化]：为这块输出建立形状为 \[BLOCK_M,BLOCK_N\] 的 FP32 accumulator，并初始化为零。它的两个轴对应输出行和输出列，不包含 K 轴。
 • [T#B#每轮加载]：在当前 K 段，加载 A 的 \[BLOCK_M,BLOCK_K\] 块以及 B 的 \[BLOCK_K,BLOCK_N\] 块；两者共享同一段 K 坐标。
-• [T#B#乘加与推进]：两块相乘得到 \[BLOCK_M,BLOCK_N\] 的部分和并加入 accumulator，然后把 A 的列基址和 B 的行基址各推进 BLOCK_K；输出行列坐标保持不变。
+• [T#B#乘加与推进]：两块相乘得到 \[BLOCK_M,BLOCK_N\] 的部分和并加入 accumulator；随后 A、B 的读取位置都沿 K 轴前进 BLOCK_K 个元素（对 A 是移到后面的列，对 B 是移到后面的行），输出行列坐标保持不变。
 • [T#B#完成输出]：遍历全部 K 段后，accumulator 才包含完整点积，可以写回该 program 负责的 C 块。
-[T#B,!c47f17#边界]：K 尾部不足整块时，越界输入应补零，避免污染点积；M/N 尾部的无效输出不写回。FP16 输入配 FP32 累加是一种精度选择，并不是上述分块数据流的数学前提。</t>
+[T#B,!c47f17#边界]：K 不是 BLOCK_K 的整数倍时，最后一段越界的 K 位置要在 load 时补零；超出 M/N 的输出位置在写回时丢弃。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -63,20 +63,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 Triton 分块矩阵乘法中，offs_k=tl.arange(0,BLOCK_K) 表示块内 K 偏移。若 K 循环通过移动 A/B 指针基址推进，offs_k 本身会怎样变化？</t>
+          <t xml:space="preserve">Triton 分块矩阵乘法的 K 循环里，offs_k=tl.arange(0,BLOCK_K) 是块内的局部 K 偏移，每轮结束时把 A、B 的指针沿 K 推进 BLOCK_K。为什么 K 尾部的 load mask 不能直接写成 offs_k&lt;K？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：offs_k 本身保持不变；每轮变化的是 A/B 指针基址，因此同一组局部偏移会指向不同的全局 K 坐标。
-• [T#B#通用关系]：将循环轮次记作 t，从 0 开始计数，则该轮全局 K 坐标为 t×BLOCK_K+offs_k；局部 offsets 始终是 0 到 BLOCK_K−1。
-• [T#B#具体例子]：BLOCK_K=4 时，第二轮 t=1：offs_k 仍为 \[0,1,2,3\]，指针指向的全局 K 坐标则为 \[4,5,6,7\]。
-[T#B,!c47f17#边界]：如果总长度 K=5，第二轮只有全局坐标 4 有效，5、6、7 必须在 load 时屏蔽并补零。这里讨论的是移动指针基址的循环写法，不能把局部偏移和全局坐标混称为同一个量。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 offs_k 是不随轮次变化的局部偏移，而 mask 要判断的是全局 K 坐标：第 t 轮（t 从 0 计）的全局坐标是 t×BLOCK_K+offs_k，正确条件是 t×BLOCK_K+offs_k&lt;K，即 offs_k&lt;K−t×BLOCK_K。
+• [T#B#局部与全局]：指针推进后，同一组 offs_k=\[0,…,BLOCK_K−1\] 每轮指向不同的全局 K 坐标；变化的是指针基址，不是 offs_k 本身。
+• [T#B#写错的后果]：offs_k&lt;K 只在第 0 轮与全局条件一致。例如 BLOCK_K=4、K=5：第 1 轮 offs_k 仍为 \[0,1,2,3\]，全部小于 5，全局坐标 5、6、7 的越界位置没有被屏蔽，读到的错误值会进入有效输出的累加。
+[T#B,!c47f17#边界]：只有 K 大于 BLOCK_K 且不是它的整数倍时，这个错误才会暴露；所以测试要有专门触发 K 尾部的 shape，例如 K=40、BLOCK_K=32。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">局部偏移不变，K 基址推进</t>
+          <t xml:space="preserve">mask 比全局 K 坐标，不比局部偏移</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -140,16 +140,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 矩阵乘法把输出划成 4 行、3 列的 tile 网格，并按 GROUP_SIZE_M=2 做 grouped PID 映射。第一组中，递增的 PID 怎样对应到输出 tile 坐标？</t>
+          <t xml:space="preserve">Triton 官方 matmul 教程在单个 GEMM 内重排 PID（grouped ordering）。输出 tile 网格为 4 行×3 列、GROUP_SIZE_M=2 时，第一组里 PID 递增，输出 tile 坐标按什么规律变化？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：在同一组内，先遍历组内的 M 行，再切换到下一个 N 列；因此第一组依次处理 (0,0)、(1,0)、(0,1)、(1,1)、(0,2)、(1,2)。
-• [T#B#坐标约定]：每个坐标写作 (输出 tile 行号,输出 tile 列号)，不是原矩阵中的单个元素坐标。这里第一组覆盖 tile 行 0、1，组高为 2。
-• [T#B#映射规律]：把组内线性编号记作 p，实际组高记作 h，则组内行号为 p%h，输出 tile 列号为 p//h；全局行号还需加上该组起始 tile 行号。
-• [T#B#复用关系]：pid=2 和 pid=3 分别负责 (0,1)、(1,1)：输出行不同、输出列相同，因此在相同 K 段需要同一个 B 列 tile。
-[T#B,!c47f17#边界]：这里描述的是线性 PID 到输出坐标的映射，不是 GPU 执行完成顺序的保证。最后一组若不足两行，必须改用实际组高。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：组内 PID 先沿 M 方向让 tile 行号递增、走完组高后，再换到下一个 tile 列（N 方向）：第一组依次处理 (0,0)、(1,0)、(0,1)、(1,1)、(0,2)、(1,2)。
+• [T#B#坐标约定]：坐标写作 (输出 tile 行号,输出 tile 列号)，不是原矩阵中的单个元素坐标；第一组覆盖 tile 行 0、1，组高为 2。
+• [T#B#映射规律]：把组内线性编号记作 p、实际组高记作 h，则组内行号为 p%h，tile 列号为 p//h；全局行号还需加上该组起始 tile 行号。
+• [T#B#复用关系]：相邻的 pid=2、3 负责 (0,1)、(1,1)：输出行不同、输出列相同，因此在相同 K 段读同一块 B 列 tile。
+[T#B,!c47f17#边界]：这是线性 PID 到输出坐标的映射，不保证 GPU 按这个顺序执行完成；最后一组不足两行时，h 要改用实际组高。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -171,7 +171,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：因为最后一组实际存在的行变少，组内 PID 对行号取模、对列号整除时也必须使用这个实际组高，否则会同时出现越界 tile 和遗漏 tile。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为尾组实际只有剩下的 tile 行：组内行号用 p%h、列号用 p//h 计算（p 是组内线性编号），h 必须取尾组的实际组高；若仍用设定组高，就会映射出不存在的 tile，同时漏掉必须计算的 tile。
 • [T#B#实际组高]：设 tile 总行数为 num_pid_m，当前组的起始 tile 行号为 first_pid_m，则实际组高是 min(GROUP_SIZE_M,num_pid_m−first_pid_m)。
 • [T#B#具体例子]：tile 网格有 5 行、3 列，设定组高为 2。前两组覆盖行 0–3，尾组只有行 4，所以剩余 pid=12、13、14 应依次映射到 (4,0)、(4,1)、(4,2)。
 • [T#B#错误后果]：若尾组仍按两行计算，pid=13 会被映射到不存在的 (5,0)，pid=14 只到 (4,1)，导致必须计算的 (4,2) 没有 program 负责。
@@ -197,11 +197,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 tile 大小同时改变数据复用、无效工作量和硬件资源占用；program 更少或循环更短，只减少了部分开销，并不等于总延迟更低。
-• [T#B#边界工作量]：M/N 尾部不满时，大 tile 可能让更多输出位置参与计算却最终不写回；仅数 program 个数会忽略这些额外工作。
-• [T#B#资源占用]：更大的输出 tile 需要更大的 accumulator，可能提高寄存器占用，使能够同时驻留的 program/warp 变少。这会改变隐藏访存或执行延迟的机会，不能只根据输出块更大就判断更快。
-• [T#B#配置共同作用]：数据复用、warps/stages、GPU 架构和编译结果都会影响实际瓶颈；同样的 M/N/K 在不同配置和设备上可能得到不同胜负。
-[T#B,!c47f17#边界]：shape 分析适合筛选候选和提出预测。最终判断应在目标 GPU 上、相同输入和可比计时条件下测量，不能仅用“M/N 大、K 小”宣布某组配置更快。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为 tile 大小同时改变复用收益，以及边界浪费和资源占用两类代价；program 更少或 K 循环更短只反映了部分开销，不等于总延迟更低。
+• [T#B#复用收益]：\[BLOCK_M,BLOCK_K\]×\[BLOCK_K,BLOCK_N\] 的一次块乘里，每个 A 元素参与 BLOCK_N 次乘加、每个 B 元素参与 BLOCK_M 次；tile 越大，每次加载的数据用得越多。
+• [T#B#边界浪费]：M/N 尾部不满时，大 tile 会多算不写回的位置。例如 M=N=130：128×128 tile 只要 4 个 program，名义输出却有 65,536 个；64×64 tile 要 9 个，名义输出 36,864 个；有效输出都是 16,900 个。
+• [T#B#资源占用]：更大的输出 tile 需要更大的 accumulator，可能提高寄存器占用，让同时驻留的 program/warp 变少，隐藏访存与执行延迟的机会也随之减少。
+[T#B,!c47f17#边界]：warps/stages、GPU 架构和编译结果也会改变实际瓶颈；shape 分析只适合筛选候选和提出预测，最终以目标 GPU 上相同输入、可比计时条件下的测量为准。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -218,51 +218,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">比较同一矩阵乘法的两种 GROUP_SIZE_M 配置时，若多轮 benchmark 无法把配置造成的耗时差异与 GPU 运行状态漂移稳定区分，应该怎样表述性能结论？</t>
+          <t xml:space="preserve">在单个 GEMM 内，grouped ordering 只重排线性 PID 到输出 tile 的映射。为什么这样可能提高 GPU 的 L2 cache 命中率并加速分块矩阵乘法？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：应表述为：在当前设备、输入形状、launch 配置和测量方法下，证据不足以稳定区分两种分组配置的性能。
-• [T#B#为何证据不足]：运行状态随时间变化本身就会改变耗时；如果这种变化与配置间的差异混在一起，就不能把观测到的快慢可靠归因于 GROUP_SIZE_M。
-• [T#B#不能推出什么]：既不能据此宣布某个配置更快，也不能说“真实影响很小”。看不清一个差异，可能是测量噪声太大，而不是差异本身很小。
-[T#B,!c47f17#边界]：结论必须限定在已经测量的条件内；更换设备、shape 或测量方法后，需要重新验证，而不能把此次“分不出来”推广为普遍无收益。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它让需要相同 A/B 输入 tile 的 program 在映射上更接近，缩短数据再次被访问的间隔；如果数据此时仍在 L2 中，就可能减少重复从显存读取的流量。
+• [T#B#复用机会]：同一输出 tile 列的不同行，会在相同 K 段使用同一个 B tile；同一输出 tile 行的不同列，也会使用相同 A tile。分组排序尝试让这些复用更及时。
+• [T#B#缓存条件]：“访问间隔短”必须短到数据尚未被其他访问从 L2 淘汰，才可能转化为命中收益。
+• [T#B#何时更有帮助]：二维 tile 网格较大、留有重排空间，计算对访存较敏感，且 group size 与并发窗口（同时活跃的那一小批 program）、block 配置和目标架构匹配时，减少显存流量更有机会降低耗时。
+[T#B,!c47f17#边界]：PID 映射不强制实际调度顺序；L2 容量和并发访问也会改变数据驻留。因此 grouped ordering 不能保证每次更快，更不能推出 group size 越大越快。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">分不出来，不等于差异很小</t>
+          <t xml:space="preserve">复用赶在 L2 淘汰之前</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 03 · 8/19 实践记录 · ABBA 结果</t>
+          <t xml:space="preserve">Lesson 03 · 8/19 实践记录 · grouped ordering</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">分块矩阵乘法中，grouped ordering 通过重排线性 PID 到输出 tile 的映射，为什么可能提高 GPU 的 L2 cache 命中率并加速计算？</t>
+          <t xml:space="preserve">Triton 官方 matmul 教程用一个例子说明单个 GEMM 内的 grouped ordering：A、B 都是 9×9 个 block，要算出最先的 9 个输出 block。按 row-major 顺序需要加载 90 个输入 block，按每组 3 个 tile 行的 grouped ordering 只需 54 个。这两个数分别怎样数出来？差距来自哪里？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它让需要相同 A/B 输入 tile 的 program 在映射上更接近，缩短数据再次被访问的间隔；如果数据此时仍在 L2 中，就可能减少重复从显存读取的流量。
-• [T#B#复用机会]：同一输出 tile 列的不同行，会在相同 K 段使用同一个 B tile；同一输出 tile 行的不同列，也会使用相同 A tile。分组排序尝试让这些复用更及时。
-• [T#B#缓存条件]：“访问间隔短”必须短到数据尚未被其他访问从 L2 淘汰，才可能转化为命中收益。较大的二维 tile 网格提供更多重排空间。
-• [T#B#何时更有帮助]：当计算对访存较敏感，且 group size 与并发窗口、block 配置和目标架构匹配时，减少显存流量更有机会降低耗时。
-[T#B,!c47f17#边界]：PID 映射不强制实际调度顺序；L2 容量和并发访问也会改变数据驻留。因此 grouped ordering 不能保证每次更快，更不能推出 group size 越大越快。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：输出 block (i,j) 需要 A 的第 i 个 tile 行和 B 的第 j 个 tile 列；一批输出覆盖的不同 tile 行数加不同 tile 列数越少，要加载的输入 block 就越少。row-major 的 9 个输出排成 1×9，分组后排成 3×3。
+• [T#B#计数单位]：A、B 都是 9×9 个 block，所以一个 A tile 行或一个 B tile 列各含沿 K 方向的 9 个 block。
+• [T#B#row-major]：前 9 个输出 block 同在第 0 个 tile 行：需要 1 个 A tile 行和全部 9 个 B tile 列，共 9+81=90 个。
+• [T#B#grouped]：每组 3 个 tile 行、组内先沿 M，前 9 个输出 block 是左上的 3×3：需要 3 个 A tile 行和 3 个 B tile 列，共 27+27=54 个。
+[T#B,!c47f17#边界]：这是假设每个不同的输入 block 只加载一次的理想化计数；实际能省多少显存流量，还要看这些 block 被再次使用时是否仍在 L2 中。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">复用赶在 L2 淘汰之前</t>
+          <t xml:space="preserve">覆盖的行数加列数越少，输入 block 越少</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 03 · 8/19 实践记录 · grouped ordering</t>
+          <t xml:space="preserve">Lesson 03 · 8/19 实践记录 · grouped ordering 访存对比</t>
         </is>
       </c>
     </row>
